--- a/SourceData/Datas/chat.xlsx
+++ b/SourceData/Datas/chat.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,7 +581,6 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>那一夜，灾兽的阴影压过诸界。你挡在最后一道光前——光留下了，心跳却没有。</t>
@@ -603,7 +602,6 @@
       <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>铠甲碎裂的瞬间，痛从喉间涌上来。名字、故土、脸上的人……像镜面裂开，一块块掉进黑暗。</t>
@@ -625,7 +623,6 @@
       <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>虚空的风暴卷住你往下坠。意识灭掉之前，胸口还留着一缕微光——细得像不肯灭的执念。</t>
@@ -647,7 +644,6 @@
       <c r="D9" t="n">
         <v>4</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>再睁眼时，是草香、泥土，和一盏暖灯。溪谷的女孩露穗在你坠落处蹲下，不问来处，只把你拖回窗边的小屋。</t>
@@ -669,7 +665,6 @@
       <c r="D10" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>伤会好，土也会暖。你和露穗在微光溪谷里翻垄、浇水——把记不得的人生，一点点种回地里。</t>
@@ -701,7 +696,6 @@
           <t>醒了？……别急着坐起来。伤要是还隐隐作痛，就靠着枕。溪谷的风软，会慢慢把人哄稳。</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" t="n">
@@ -723,7 +717,6 @@
           <t>这里是我们的小农庄。镇上的事不着急——先把院子收拾顺了，家才像个家。</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" t="n">
@@ -745,7 +738,6 @@
           <t>你看，草都快爬到脚踝了。用手拔几把吧，草料留着，后面做工具用得上。我在旁边陪你。</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" t="n">
@@ -767,7 +759,6 @@
           <t>对了，任务本和背包也给你打开了。小图标会从中间飞到右下角，点开就能用。</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" t="n">
@@ -789,7 +780,6 @@
           <t>草料够了。这把锄头先借你——会飞进背包，你再拖到下方快捷栏。多翻几块荒地；田翻好了，才能用草料搓种子。</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" t="n">
@@ -811,7 +801,6 @@
           <t>芽埋好了。田边那些石子硌脚——握着锄头挖一挖。石料攒够了，就能做水壶浇水。</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" t="n">
@@ -833,7 +822,6 @@
           <t>材料齐了。回工作台，用石料和泥土做一把水壶。没有水，芽撑不久。</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" t="n">
@@ -855,7 +843,6 @@
           <t>田翻好了。去工作台，用草料搓出种子。没有种子，土再肥也空着。</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" t="n">
@@ -877,7 +864,6 @@
           <t>种子有了。选中它们，在翻好的田上多种几棵——轻轻埋进去就行。</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" t="n">
@@ -899,7 +885,6 @@
           <t>水壶好了。选中它，给田里浇浇水——领奖时会拿到催熟剂，能让作物快点长大。</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" t="n">
@@ -921,7 +906,6 @@
           <t>把催熟剂拖进快捷栏，点作物催熟，再空手收获。多收一点，心里踏实。</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" t="n">
@@ -943,7 +927,6 @@
           <t>收成有了。再去工作台，用石料和草料做把斧头——林子里的树，该练练手了。</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="B23" t="n">
@@ -965,7 +948,6 @@
           <t>斧头沉甸甸的。选中它，去砍几棵树，攒点木料——待会儿织鱼竿要用。</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" t="n">
@@ -987,7 +969,6 @@
           <t>木料够了。回工作台，用木料和草料织鱼竿——湖那头，该尝点鲜了。</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" t="n">
@@ -1009,7 +990,6 @@
           <t>鱼竿好了。先点下方鱼竿，跟着地上的星光走到西边码头，再点水面抛竿。第一条鱼，我等着看。</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="B26" t="n">
@@ -1031,7 +1011,6 @@
           <t>湖面都静下来了。农活、工具、收获……农场这边，总算站稳了。</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" t="n">
@@ -1053,7 +1032,6 @@
           <t>该去镇上露个面了。往东走到「通往小镇」的路牌，走近点一下就能进镇。镇长府在镇北——去吧，我在这儿等你回来。</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" t="n">
@@ -1065,13 +1043,11 @@
       <c r="D28" t="n">
         <v>1</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>石板路，木瓦屋顶，广场上钟楼的影子还残着裂痕——微光溪谷镇，把迟到的你接了进来。</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="B29" t="n">
@@ -1093,7 +1069,6 @@
           <t>新来的？先去镇长府报个到。艾岚镇长这会儿多半在喝茶。</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" t="n">
@@ -1115,7 +1090,6 @@
           <t>往北找镇长府，点大门进屋，跟艾岚打个招呼。</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" t="n">
@@ -1137,7 +1111,6 @@
           <t>农庄的新主人？来，先喝口热茶。路上风硬。</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="B32" t="n">
@@ -1159,7 +1132,6 @@
           <t>农庄归你了，定居许可我也批过。溪谷不赶人——可也不养闲人。</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="B33" t="n">
@@ -1181,7 +1153,6 @@
           <t>眼下先认认镇子：公告板听听委托，木工坊去认认石楠。买卖的事，摸熟路了再教你。</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" t="n">
@@ -1203,7 +1174,6 @@
           <t>社区中心那座钟楼……等你把镇子走熟了，再去看看。我们总要把它重新点亮。</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" t="n">
@@ -1225,7 +1195,6 @@
           <t>明白了。我先去公告板看看。</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" t="n">
@@ -1247,7 +1216,6 @@
           <t>去警察局或邮局的公告板接一单——听听镇上最近在忙什么。</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" t="n">
@@ -1269,7 +1237,6 @@
           <t>木工坊在东市。石楠管修路、扩建——钉子和木料的事，问他就对了。</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" t="n">
@@ -1291,7 +1258,6 @@
           <t>去社区中心，那座破旧钟楼。看看修复还缺什么。</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" t="n">
@@ -1313,7 +1279,6 @@
           <t>新邻居？锤子搁这儿。扩建农舍、修南路，材料齐了随时来找我。</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" t="n">
@@ -1335,7 +1300,6 @@
           <t>社区中心那堆烂梁我也看过。镇长若立项，我跟进。你先去钟楼转一圈。</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" t="n">
@@ -1357,7 +1321,6 @@
           <t>好，我去社区中心看看。</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" t="n">
@@ -1379,7 +1342,6 @@
           <t>欢迎。钟楼积了灰，脚手架还堆在墙角——工程像被人忽然叫停。</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" t="n">
@@ -1401,7 +1363,6 @@
           <t>先认得这厅堂就好。材料凑齐了，春厅会重新亮起来。</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" t="n">
@@ -1423,7 +1384,6 @@
           <t>记下了。回头再来。</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" t="n">
@@ -1435,13 +1395,11 @@
       <c r="D45" t="n">
         <v>4</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>钟楼的线索接到了。领完奖励，镇长会教你在市集买卖。</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" t="n">
@@ -1463,7 +1421,6 @@
           <t>（信件）站稳了就好。下一章从市集开始——先买一件日用，再把背包里的收获卖掉一单。手熟了，再谈春厅。</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" t="n">
@@ -1485,7 +1442,6 @@
           <t>任意一家店买一件东西就好，熟个手。种子店、杂货铺都行。</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" t="n">
@@ -1507,7 +1463,6 @@
           <t>买过就会卖。打开商店点「出售」，把防风草或鱼卖掉一件——金币进袋，才算真正进了市集。</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" t="n">
@@ -1529,7 +1484,6 @@
           <t>买卖摸熟了。回社区中心——春厅收集包该签字立项了。</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" t="n">
@@ -1541,13 +1495,11 @@
       <c r="D50" t="n">
         <v>1</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>木桌上摊着一份「春厅收集包」名册，墨迹未干，旁边压着一枚镇徽章。</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" t="n">
@@ -1569,7 +1521,6 @@
           <t>（字条）先签你的名字。春厅要亮，得有钉子、药草和铜——诊所与矿脉商会那边，你去打个招呼。</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" t="n">
@@ -1591,7 +1542,6 @@
           <t>签上了。下一步，先去微光诊所。</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" t="n">
@@ -1613,7 +1563,6 @@
           <t>去微光诊所。下矿前，先听听医生的叮嘱。</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" t="n">
@@ -1635,7 +1584,6 @@
           <t>新邻居？手伸过来——脉象还稳。矿洞里潮、暗、滑，别逞强。</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" t="n">
@@ -1657,7 +1605,6 @@
           <t>浅层铜脉可以碰。要是头晕耳鸣，立刻上来找我。伤药回头再备。</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" t="n">
@@ -1679,7 +1626,6 @@
           <t>明白了。接下来去矿脉商会拿通行证。</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" t="n">
@@ -1701,7 +1647,6 @@
           <t>去矿脉商会——矿石店那家。打听浅层矿洞放行的事。</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" t="n">
@@ -1723,7 +1668,6 @@
           <t>商会放行了。去北山路牌，进浅层矿洞。</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" t="n">
@@ -1745,7 +1689,6 @@
           <t>选中锄头，把洞里的铜矿石挖下来——先采三块带回镇上。</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" t="n">
@@ -1767,7 +1710,6 @@
           <t>铜够了。回社区中心，把第一袋矿交给春厅。</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" t="n">
@@ -1779,13 +1721,11 @@
       <c r="D61" t="n">
         <v>1</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>你把铜矿搁上木台。钟楼角落一盏旧灯忽然亮起——微弱，却稳。</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" t="n">
@@ -1807,7 +1747,6 @@
           <t>春厅有光了。后面还有钉子、药草和南路……不急。溪谷会记着你这一袋铜。</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" t="n">
@@ -1829,7 +1768,6 @@
           <t>市集和春厅都站住了。领完奖励，可以再转转镇子，或者回农场。</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" t="n">
@@ -1851,7 +1789,6 @@
           <t>（信件）买卖熟了，春厅也亮了。南路与海滩的事，等社区再凑齐一批材料再说。慢慢来。</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" t="n">
@@ -1873,7 +1810,6 @@
           <t>嗯？找我呀。</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" t="n">
@@ -1895,7 +1831,72 @@
           <t>不着急，一步一步来。今天也好好过——有我在。</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>62</v>
+      </c>
+      <c r="C67" t="n">
+        <v>10036</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>掌柜·赤铜</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>打听浅层矿洞？诊所叮嘱听过就好。商会给你一纸放行——北山路牌认这个。</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>63</v>
+      </c>
+      <c r="C68" t="n">
+        <v>10036</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>掌柜·赤铜</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>洞口不深，铜脉够春厅第一袋。采回来的矿石也能在这儿出手。</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>64</v>
+      </c>
+      <c r="C69" t="n">
+        <v>10036</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>你</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>领到通行证了。接下来去北山路牌。</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SourceData/Datas/chat.xlsx
+++ b/SourceData/Datas/chat.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chat" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="chat" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,10 +678,10 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>10002</v>
+        <v>10004</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -693,19 +693,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>醒了？……别急着坐起来。伤要是还隐隐作痛，就靠着枕。溪谷的风软，会慢慢把人哄稳。</t>
+          <t>芽埋好了。田边那些石子硌脚——握着锄头挖一挖。石料攒够了，就能做水壶浇水。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>10002</v>
+        <v>10005</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -714,19 +714,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>这里是我们的小农庄。镇上的事不着急——先把院子收拾顺了，家才像个家。</t>
+          <t>材料齐了。回工作台，用石料和泥土做一把水壶。没有水，芽撑不久。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>10002</v>
+        <v>10006</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -735,19 +735,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>你看，草都快爬到脚踝了。用手拔几把吧，草料留着，后面做工具用得上。我在旁边陪你。</t>
+          <t>田翻好了。去工作台，用草料搓出种子。没有种子，土再肥也空着。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>10002</v>
+        <v>10010</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -756,16 +756,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>对了，任务本和背包也给你打开了。小图标会从中间飞到右下角，点开就能用。</t>
+          <t>收成有了。再去工作台，用石料和草料做把斧头——林子里的树，该练练手了。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>10003</v>
+        <v>10012</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -777,326 +777,326 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>草料够了。这把锄头先借你——会飞进背包，你再拖到下方快捷栏。多翻几块荒地；田翻好了，才能用草料搓种子。</t>
+          <t>木料够了。回工作台，用木料和草料织鱼竿——湖那头，该尝点鲜了。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C16" t="n">
-        <v>10004</v>
+        <v>10016</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>露穗</t>
+          <t>镇长·艾岚</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>芽埋好了。田边那些石子硌脚——握着锄头挖一挖。石料攒够了，就能做水壶浇水。</t>
+          <t>农庄的新主人？来，先喝口热茶。路上风硬。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C17" t="n">
-        <v>10005</v>
+        <v>10016</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>露穗</t>
+          <t>镇长·艾岚</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>材料齐了。回工作台，用石料和泥土做一把水壶。没有水，芽撑不久。</t>
+          <t>农庄归你了，定居许可我也批过。溪谷不赶人——可也不养闲人。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C18" t="n">
-        <v>10006</v>
+        <v>10016</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>露穗</t>
+          <t>镇长·艾岚</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>田翻好了。去工作台，用草料搓出种子。没有种子，土再肥也空着。</t>
+          <t>眼下先认认镇子：公告板听听委托，木工坊去认认石楠。买卖的事，摸熟路了再教你。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C19" t="n">
-        <v>10007</v>
+        <v>10016</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>露穗</t>
+          <t>镇长·艾岚</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>种子有了。选中它们，在翻好的田上多种几棵——轻轻埋进去就行。</t>
+          <t>社区中心那座钟楼……等你把镇子走熟了，再去看看。我们总要把它重新点亮。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C20" t="n">
-        <v>10008</v>
+        <v>10016</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>露穗</t>
+          <t>你</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>水壶好了。选中它，给田里浇浇水——领奖时会拿到催熟剂，能让作物快点长大。</t>
+          <t>明白了。我先去公告板看看。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>10009</v>
+        <v>10017</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>露穗</t>
+          <t>你</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>把催熟剂拖进快捷栏，点作物催熟，再空手收获。多收一点，心里踏实。</t>
+          <t>去警察局或邮局的公告板接一单——听听镇上最近在忙什么。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C22" t="n">
-        <v>10010</v>
+        <v>10018</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>露穗</t>
+          <t>镇长·艾岚</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>收成有了。再去工作台，用石料和草料做把斧头——林子里的树，该练练手了。</t>
+          <t>木工坊在东市。石楠管修路、扩建——钉子和木料的事，问他就对了。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>10011</v>
+        <v>10019</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>露穗</t>
+          <t>你</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>斧头沉甸甸的。选中它，去砍几棵树，攒点木料——待会儿织鱼竿要用。</t>
+          <t>去社区中心，那座破旧钟楼。看看修复还缺什么。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C24" t="n">
-        <v>10012</v>
+        <v>10020</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>露穗</t>
+          <t>工匠·石楠</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>木料够了。回工作台，用木料和草料织鱼竿——湖那头，该尝点鲜了。</t>
+          <t>新邻居？锤子搁这儿。扩建农舍、修南路，材料齐了随时来找我。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C25" t="n">
-        <v>10013</v>
+        <v>10020</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>露穗</t>
+          <t>工匠·石楠</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>鱼竿好了。先点下方鱼竿，跟着地上的星光走到西边码头，再点水面抛竿。第一条鱼，我等着看。</t>
+          <t>社区中心那堆烂梁我也看过。镇长若立项，我跟进。你先去钟楼转一圈。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C26" t="n">
-        <v>10014</v>
+        <v>10020</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>露穗</t>
+          <t>你</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>湖面都静下来了。农活、工具、收获……农场这边，总算站稳了。</t>
+          <t>好，我去社区中心看看。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C27" t="n">
-        <v>10014</v>
+        <v>10021</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>露穗</t>
+          <t>管理员·苔青</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>该去镇上露个面了。往东走到「通往小镇」的路牌，走近点一下就能进镇。镇长府在镇北——去吧，我在这儿等你回来。</t>
+          <t>欢迎。钟楼积了灰，脚手架还堆在墙角——工程像被人忽然叫停。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C28" t="n">
-        <v>10015</v>
+        <v>10021</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>管理员·苔青</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>石板路，木瓦屋顶，广场上钟楼的影子还残着裂痕——微光溪谷镇，把迟到的你接了进来。</t>
+          <t>先认得这厅堂就好。材料凑齐了，春厅会重新亮起来。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C29" t="n">
-        <v>10015</v>
+        <v>10021</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>路人</t>
+          <t>你</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>新来的？先去镇长府报个到。艾岚镇长这会儿多半在喝茶。</t>
+          <t>记下了。回头再来。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C30" t="n">
-        <v>10015</v>
+        <v>10021</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>你</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>往北找镇长府，点大门进屋，跟艾岚打个招呼。</t>
+          <t>钟楼的线索接到了。领完奖励，镇长会教你在市集买卖。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C31" t="n">
-        <v>10016</v>
+        <v>10022</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
@@ -1108,19 +1108,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>农庄的新主人？来，先喝口热茶。路上风硬。</t>
+          <t>（信件）站稳了就好。下一章从市集开始——先买一件日用，再把背包里的收获卖掉一单。手熟了，再谈春厅。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C32" t="n">
-        <v>10016</v>
+        <v>10023</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1129,19 +1129,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>农庄归你了，定居许可我也批过。溪谷不赶人——可也不养闲人。</t>
+          <t>任意一家店买一件东西就好，熟个手。种子店、杂货铺都行。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C33" t="n">
-        <v>10016</v>
+        <v>10024</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1150,100 +1150,95 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>眼下先认认镇子：公告板听听委托，木工坊去认认石楠。买卖的事，摸熟路了再教你。</t>
+          <t>买过就会卖。打开商店点「出售」，把防风草或鱼卖掉一件——金币进袋，才算真正进了市集。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C34" t="n">
-        <v>10016</v>
+        <v>10025</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>镇长·艾岚</t>
+          <t>你</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>社区中心那座钟楼……等你把镇子走熟了，再去看看。我们总要把它重新点亮。</t>
+          <t>买卖摸熟了。回社区中心——春厅收集包该签字立项了。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C35" t="n">
-        <v>10016</v>
+        <v>10026</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>你</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>明白了。我先去公告板看看。</t>
+          <t>木桌上摊着一份「春厅收集包」名册，墨迹未干，旁边压着一枚镇徽章。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C36" t="n">
-        <v>10017</v>
+        <v>10026</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>你</t>
+          <t>镇长·艾岚</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>去警察局或邮局的公告板接一单——听听镇上最近在忙什么。</t>
+          <t>（字条）先签你的名字。春厅要亮，得有钉子、药草和铜——诊所与矿脉商会那边，你去打个招呼。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C37" t="n">
-        <v>10018</v>
+        <v>10026</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>镇长·艾岚</t>
+          <t>你</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>木工坊在东市。石楠管修路、扩建——钉子和木料的事，问他就对了。</t>
+          <t>签上了。下一步，先去微光诊所。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C38" t="n">
-        <v>10019</v>
+        <v>10027</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
@@ -1255,58 +1250,58 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>去社区中心，那座破旧钟楼。看看修复还缺什么。</t>
+          <t>去微光诊所。下矿前，先听听医生的叮嘱。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C39" t="n">
-        <v>10020</v>
+        <v>10028</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>工匠·石楠</t>
+          <t>医生·荷叶</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>新邻居？锤子搁这儿。扩建农舍、修南路，材料齐了随时来找我。</t>
+          <t>新邻居？手伸过来——脉象还稳。矿洞里潮、暗、滑，别逞强。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C40" t="n">
-        <v>10020</v>
+        <v>10028</v>
       </c>
       <c r="D40" t="n">
         <v>2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>工匠·石楠</t>
+          <t>医生·荷叶</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>社区中心那堆烂梁我也看过。镇长若立项，我跟进。你先去钟楼转一圈。</t>
+          <t>浅层铜脉可以碰。要是头晕耳鸣，立刻上来找我。伤药回头再备。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C41" t="n">
-        <v>10020</v>
+        <v>10028</v>
       </c>
       <c r="D41" t="n">
         <v>3</v>
@@ -1318,61 +1313,61 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>好，我去社区中心看看。</t>
+          <t>明白了。接下来去矿脉商会拿通行证。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C42" t="n">
-        <v>10021</v>
+        <v>10029</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>管理员·苔青</t>
+          <t>你</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>欢迎。钟楼积了灰，脚手架还堆在墙角——工程像被人忽然叫停。</t>
+          <t>去矿脉商会——矿石店那家。打听浅层矿洞放行的事。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C43" t="n">
-        <v>10021</v>
+        <v>10030</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>管理员·苔青</t>
+          <t>你</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>先认得这厅堂就好。材料凑齐了，春厅会重新亮起来。</t>
+          <t>商会放行了。去北山路牌，进浅层矿洞。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C44" t="n">
-        <v>10021</v>
+        <v>10032</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1381,35 +1376,35 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>记下了。回头再来。</t>
+          <t>铜够了。回社区中心，把第一袋矿交给春厅。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C45" t="n">
-        <v>10021</v>
+        <v>10033</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>钟楼的线索接到了。领完奖励，镇长会教你在市集买卖。</t>
+          <t>你把铜矿搁上木台。钟楼角落一盏旧灯忽然亮起——微弱，却稳。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="C46" t="n">
-        <v>10022</v>
+        <v>10033</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1418,116 +1413,121 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>（信件）站稳了就好。下一章从市集开始——先买一件日用，再把背包里的收获卖掉一单。手熟了，再谈春厅。</t>
+          <t>春厅有光了。后面还有钉子、药草和南路……不急。溪谷会记着你这一袋铜。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C47" t="n">
-        <v>10023</v>
+        <v>10033</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>镇长·艾岚</t>
+          <t>你</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>任意一家店买一件东西就好，熟个手。种子店、杂货铺都行。</t>
+          <t>市集和春厅都站住了。领完奖励，可以再转转镇子，或者回农场。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C48" t="n">
-        <v>10024</v>
+        <v>10035</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>镇长·艾岚</t>
+          <t>露穗</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>买过就会卖。打开商店点「出售」，把防风草或鱼卖掉一件——金币进袋，才算真正进了市集。</t>
+          <t>嗯？找我呀。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C49" t="n">
-        <v>10025</v>
+        <v>10035</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>你</t>
+          <t>露穗</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>买卖摸熟了。回社区中心——春厅收集包该签字立项了。</t>
+          <t>不着急，一步一步来。今天也好好过——有我在。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="C50" t="n">
-        <v>10026</v>
+        <v>10036</v>
       </c>
       <c r="D50" t="n">
         <v>1</v>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>掌柜·赤铜</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>木桌上摊着一份「春厅收集包」名册，墨迹未干，旁边压着一枚镇徽章。</t>
+          <t>打听浅层矿洞？诊所叮嘱听过就好。商会给你一纸放行——北山路牌认这个。</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C51" t="n">
-        <v>10026</v>
+        <v>10036</v>
       </c>
       <c r="D51" t="n">
         <v>2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>镇长·艾岚</t>
+          <t>掌柜·赤铜</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>（字条）先签你的名字。春厅要亮，得有钉子、药草和铜——诊所与矿脉商会那边，你去打个招呼。</t>
+          <t>洞口不深，铜脉够春厅第一袋。采回来的矿石也能在这儿出手。</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C52" t="n">
-        <v>10026</v>
+        <v>10036</v>
       </c>
       <c r="D52" t="n">
         <v>3</v>
@@ -1539,263 +1539,268 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>签上了。下一步，先去微光诊所。</t>
+          <t>领到通行证了。接下来去北山路牌。</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="C53" t="n">
-        <v>10027</v>
+        <v>10034</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>你</t>
+          <t>镇长·艾岚</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>去微光诊所。下矿前，先听听医生的叮嘱。</t>
+          <t>春厅亮了，矿脉也稳了。下一步把南路修通，去海滩听听潮声——这不是终局，溪谷还在等你。</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C54" t="n">
-        <v>10028</v>
+        <v>10002</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>医生·荷叶</t>
+          <t>露穗</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>新邻居？手伸过来——脉象还稳。矿洞里潮、暗、滑，别逞强。</t>
+          <t>醒了？……别急着坐起来。伤要是还隐隐作痛，就靠着枕。溪谷的风软，会慢慢把人哄稳。</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="C55" t="n">
-        <v>10028</v>
+        <v>10002</v>
       </c>
       <c r="D55" t="n">
         <v>2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>医生·荷叶</t>
+          <t>露穗</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>浅层铜脉可以碰。要是头晕耳鸣，立刻上来找我。伤药回头再备。</t>
+          <t>这里是我们的小农庄。镇上的事不着急——先把院子收拾顺了，家才像个家。</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C56" t="n">
-        <v>10028</v>
+        <v>10002</v>
       </c>
       <c r="D56" t="n">
         <v>3</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>你</t>
+          <t>露穗</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>明白了。接下来去矿脉商会拿通行证。</t>
+          <t>你看，草都快爬到脚踝了。拔几把吧，草料留着，后面做工具用得上。我在旁边陪你。</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="C57" t="n">
-        <v>10029</v>
+        <v>10002</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>你</t>
+          <t>露穗</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>去矿脉商会——矿石店那家。打听浅层矿洞放行的事。</t>
+          <t>对了，院子里的事我帮你记着；要用的东西也放你身边了——随时翻就行。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C58" t="n">
-        <v>10030</v>
+        <v>10003</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>你</t>
+          <t>露穗</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>商会放行了。去北山路牌，进浅层矿洞。</t>
+          <t>草拔得差不多啦。这把锄头先借你，先拿着。</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C59" t="n">
-        <v>10031</v>
+        <v>10003</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>你</t>
+          <t>露穗</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>选中锄头，把洞里的铜矿石挖下来——先采三块带回镇上。</t>
+          <t>把院子里的荒地翻几垄。土松了，才能拿草料搓种子。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="C60" t="n">
-        <v>10032</v>
+        <v>10007</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>你</t>
+          <t>露穗</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>铜够了。回社区中心，把第一袋矿交给春厅。</t>
+          <t>种子有了。翻好的田空着可惜，多种几棵进去——轻轻埋实就行。</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C61" t="n">
-        <v>10033</v>
+        <v>10008</v>
       </c>
       <c r="D61" t="n">
         <v>1</v>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>露穗</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>你把铜矿搁上木台。钟楼角落一盏旧灯忽然亮起——微弱，却稳。</t>
+          <t>水壶好了，给秧苗浇透吧。浇完今晚歇一夜，明早才能收。赶路的时候，催熟剂也能让芽连夜长。</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="C62" t="n">
-        <v>10033</v>
+        <v>10037</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>镇长·艾岚</t>
+          <t>露穗</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>春厅有光了。后面还有钉子、药草和南路……不急。溪谷会记着你这一袋铜。</t>
+          <t>天色不早了。回小屋歇一夜吧——浇过水的田，夜里会自己长。</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C63" t="n">
-        <v>10033</v>
+        <v>10009</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>你</t>
+          <t>露穗</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>市集和春厅都站住了。领完奖励，可以再转转镇子，或者回农场。</t>
+          <t>睡醒了？田里的菜已经长好了，摘回来就行。催熟剂以后赶路再用也来得及。</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C64" t="n">
-        <v>10034</v>
+        <v>10011</v>
       </c>
       <c r="D64" t="n">
         <v>1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>镇长·艾岚</t>
+          <t>露穗</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>（信件）买卖熟了，春厅也亮了。南路与海滩的事，等社区再凑齐一批材料再说。慢慢来。</t>
+          <t>斧头沉甸甸的。去林子里砍几棵，攒点木料——待会儿织鱼竿要用。</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="C65" t="n">
-        <v>10035</v>
+        <v>10013</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
@@ -1807,19 +1812,19 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>嗯？找我呀。</t>
+          <t>鱼竿好了。去西边码头，朝水面抛一竿。第一条鱼，我等着看。</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C66" t="n">
-        <v>10035</v>
+        <v>10014</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1828,75 +1833,110 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>不着急，一步一步来。今天也好好过——有我在。</t>
+          <t>湖面都静下来了。农活、工具、收获……农场这边，总算站稳了。</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C67" t="n">
-        <v>10036</v>
+        <v>10014</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>掌柜·赤铜</t>
+          <t>露穗</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>打听浅层矿洞？诊所叮嘱听过就好。商会给你一纸放行——北山路牌认这个。</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>该去镇上露个面了。往东走到路牌那儿就能进镇。镇长府在镇北——去吧，我在这儿等你回来。</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C68" t="n">
-        <v>10036</v>
+        <v>10015</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>掌柜·赤铜</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>洞口不深，铜脉够春厅第一袋。采回来的矿石也能在这儿出手。</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>石板路，木瓦屋顶，广场上钟楼的影子还残着裂痕——微光溪谷镇，把迟到的你接了进来。</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="C69" t="n">
-        <v>10036</v>
+        <v>10015</v>
       </c>
       <c r="D69" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>路人</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>新来的？先去镇长府报个到。艾岚镇长这会儿多半在喝茶。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>85</v>
+      </c>
+      <c r="C70" t="n">
+        <v>10015</v>
+      </c>
+      <c r="D70" t="n">
         <v>3</v>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>你</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>领到通行证了。接下来去北山路牌。</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>……北头那栋就是镇长府。先去打个招呼吧。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>86</v>
+      </c>
+      <c r="C71" t="n">
+        <v>10031</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>你</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>把洞里的铜矿石挖下来——先采三块带回镇上。</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
